--- a/Input/Excel/cnt_Contract LRU.xlsx
+++ b/Input/Excel/cnt_Contract LRU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\workspace\Core\ItemClassGenerator\Input\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130D9B36-0A8F-405D-9DC9-34C5E4D996B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B76A1A0F-3560-4B63-815C-5390D131DBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3948" yWindow="2604" windowWidth="34560" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6528" yWindow="5076" windowWidth="34560" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Property" sheetId="1" r:id="rId1"/>
@@ -281,7 +281,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -308,8 +308,15 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -330,6 +337,11 @@
     <fill>
       <patternFill patternType="none"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -340,10 +352,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="justify" wrapText="1"/>
@@ -357,8 +370,19 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="justify" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="justify" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -796,16 +820,16 @@
     </row>
     <row r="2" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>19</v>
+        <v>50</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
@@ -829,7 +853,7 @@
         <v>21</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>22</v>
@@ -841,7 +865,7 @@
         <v>20</v>
       </c>
       <c r="P2" s="3">
-        <v>3584</v>
+        <v>1664</v>
       </c>
       <c r="Q2" t="s">
         <v>20</v>
@@ -861,8 +885,8 @@
       <c r="V2" t="s">
         <v>20</v>
       </c>
-      <c r="W2" s="2" t="s">
-        <v>24</v>
+      <c r="W2" t="s">
+        <v>20</v>
       </c>
       <c r="X2" t="s">
         <v>20</v>
@@ -877,18 +901,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" s="6" customFormat="1" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>28</v>
+        <v>50</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
@@ -906,13 +930,13 @@
         <v>21</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>21</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>22</v>
@@ -924,10 +948,10 @@
         <v>20</v>
       </c>
       <c r="P3" s="3">
-        <v>3712</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>2</v>
+        <v>2048</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>20</v>
       </c>
       <c r="R3" t="s">
         <v>20</v>
@@ -962,19 +986,19 @@
     </row>
     <row r="4" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="3">
-        <v>64</v>
+        <v>50</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
       </c>
       <c r="F4" t="s">
         <v>20</v>
@@ -1007,7 +1031,7 @@
         <v>20</v>
       </c>
       <c r="P4" s="3">
-        <v>3072</v>
+        <v>2560</v>
       </c>
       <c r="Q4" t="s">
         <v>20</v>
@@ -1045,19 +1069,19 @@
     </row>
     <row r="5" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="3">
-        <v>512</v>
+      <c r="E5" t="s">
+        <v>20</v>
       </c>
       <c r="F5" t="s">
         <v>20</v>
@@ -1090,7 +1114,7 @@
         <v>20</v>
       </c>
       <c r="P5" s="3">
-        <v>128</v>
+        <v>2176</v>
       </c>
       <c r="Q5" t="s">
         <v>20</v>
@@ -1128,16 +1152,16 @@
     </row>
     <row r="6" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
@@ -1173,7 +1197,7 @@
         <v>20</v>
       </c>
       <c r="P6" s="3">
-        <v>2688</v>
+        <v>512</v>
       </c>
       <c r="Q6" t="s">
         <v>20</v>
@@ -1187,8 +1211,8 @@
       <c r="T6" t="s">
         <v>20</v>
       </c>
-      <c r="U6" t="s">
-        <v>20</v>
+      <c r="U6" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="V6" t="s">
         <v>20</v>
@@ -1211,16 +1235,16 @@
     </row>
     <row r="7" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
@@ -1232,7 +1256,7 @@
         <v>20</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>21</v>
@@ -1256,7 +1280,7 @@
         <v>20</v>
       </c>
       <c r="P7" s="3">
-        <v>640</v>
+        <v>1024</v>
       </c>
       <c r="Q7" t="s">
         <v>20</v>
@@ -1270,8 +1294,8 @@
       <c r="T7" t="s">
         <v>20</v>
       </c>
-      <c r="U7" t="s">
-        <v>20</v>
+      <c r="U7" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="V7" t="s">
         <v>20</v>
@@ -1294,16 +1318,16 @@
     </row>
     <row r="8" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
@@ -1315,7 +1339,7 @@
         <v>20</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>21</v>
@@ -1327,7 +1351,7 @@
         <v>21</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>22</v>
@@ -1339,7 +1363,7 @@
         <v>20</v>
       </c>
       <c r="P8" s="3">
-        <v>512</v>
+        <v>3584</v>
       </c>
       <c r="Q8" t="s">
         <v>20</v>
@@ -1353,14 +1377,14 @@
       <c r="T8" t="s">
         <v>20</v>
       </c>
-      <c r="U8" s="2" t="s">
-        <v>40</v>
+      <c r="U8" t="s">
+        <v>20</v>
       </c>
       <c r="V8" t="s">
         <v>20</v>
       </c>
-      <c r="W8" t="s">
-        <v>20</v>
+      <c r="W8" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="X8" t="s">
         <v>20</v>
@@ -1377,13 +1401,13 @@
     </row>
     <row r="9" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
@@ -1422,7 +1446,7 @@
         <v>20</v>
       </c>
       <c r="P9" s="3">
-        <v>2304</v>
+        <v>2432</v>
       </c>
       <c r="Q9" t="s">
         <v>20</v>
@@ -1460,16 +1484,16 @@
     </row>
     <row r="10" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -1505,7 +1529,7 @@
         <v>20</v>
       </c>
       <c r="P10" s="3">
-        <v>1280</v>
+        <v>3200</v>
       </c>
       <c r="Q10" t="s">
         <v>20</v>
@@ -1542,94 +1566,94 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="N11" s="2" t="s">
+      <c r="A11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="O11" t="s">
-        <v>20</v>
-      </c>
-      <c r="P11" s="3">
-        <v>2432</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>20</v>
-      </c>
-      <c r="R11" t="s">
-        <v>20</v>
-      </c>
-      <c r="S11" t="s">
-        <v>20</v>
-      </c>
-      <c r="T11" t="s">
-        <v>20</v>
-      </c>
-      <c r="U11" t="s">
-        <v>20</v>
-      </c>
-      <c r="V11" t="s">
-        <v>20</v>
-      </c>
-      <c r="W11" t="s">
-        <v>20</v>
-      </c>
-      <c r="X11" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA11" s="2" t="s">
+      <c r="O11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="P11" s="8">
+        <v>3712</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>2</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="S11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="T11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="U11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="V11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="X11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA11" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" s="6" customFormat="1" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>27</v>
@@ -1671,7 +1695,7 @@
         <v>20</v>
       </c>
       <c r="P12" s="3">
-        <v>384</v>
+        <v>2688</v>
       </c>
       <c r="Q12" t="s">
         <v>20</v>
@@ -1709,16 +1733,16 @@
     </row>
     <row r="13" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
         <v>20</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" t="s">
-        <v>20</v>
+        <v>27</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="E13" t="s">
         <v>20</v>
@@ -1730,7 +1754,7 @@
         <v>20</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>21</v>
@@ -1754,7 +1778,7 @@
         <v>20</v>
       </c>
       <c r="P13" s="3">
-        <v>1664</v>
+        <v>640</v>
       </c>
       <c r="Q13" t="s">
         <v>20</v>
@@ -1792,16 +1816,16 @@
     </row>
     <row r="14" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>20</v>
+        <v>27</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="E14" t="s">
         <v>20</v>
@@ -1837,7 +1861,7 @@
         <v>20</v>
       </c>
       <c r="P14" s="3">
-        <v>2048</v>
+        <v>1280</v>
       </c>
       <c r="Q14" t="s">
         <v>20</v>
@@ -1874,85 +1898,85 @@
       </c>
     </row>
     <row r="15" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="3">
-        <v>128</v>
-      </c>
-      <c r="F15" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="N15" s="2" t="s">
+      <c r="A15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="O15" t="s">
-        <v>20</v>
-      </c>
-      <c r="P15" s="3">
-        <v>256</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>20</v>
-      </c>
-      <c r="R15" t="s">
-        <v>20</v>
-      </c>
-      <c r="S15" t="s">
-        <v>20</v>
-      </c>
-      <c r="T15" t="s">
-        <v>20</v>
-      </c>
-      <c r="U15" t="s">
-        <v>20</v>
-      </c>
-      <c r="V15" t="s">
-        <v>20</v>
-      </c>
-      <c r="W15" t="s">
-        <v>20</v>
-      </c>
-      <c r="X15" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA15" s="2" t="s">
+      <c r="O15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="P15" s="8">
+        <v>384</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="R15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="S15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="T15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="U15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="V15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="X15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA15" s="5" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2041,19 +2065,19 @@
     </row>
     <row r="17" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="3">
-        <v>8</v>
+        <v>27</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" t="s">
+        <v>20</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
@@ -2086,7 +2110,7 @@
         <v>20</v>
       </c>
       <c r="P17" s="3">
-        <v>1792</v>
+        <v>896</v>
       </c>
       <c r="Q17" t="s">
         <v>20</v>
@@ -2124,7 +2148,7 @@
     </row>
     <row r="18" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s">
         <v>20</v>
@@ -2133,7 +2157,7 @@
         <v>27</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="E18" t="s">
         <v>20</v>
@@ -2169,7 +2193,7 @@
         <v>20</v>
       </c>
       <c r="P18" s="3">
-        <v>896</v>
+        <v>1152</v>
       </c>
       <c r="Q18" t="s">
         <v>20</v>
@@ -2207,19 +2231,19 @@
     </row>
     <row r="19" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="3">
-        <v>8</v>
+        <v>27</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" t="s">
+        <v>20</v>
       </c>
       <c r="F19" t="s">
         <v>20</v>
@@ -2252,7 +2276,7 @@
         <v>20</v>
       </c>
       <c r="P19" s="3">
-        <v>1920</v>
+        <v>768</v>
       </c>
       <c r="Q19" t="s">
         <v>20</v>
@@ -2290,7 +2314,7 @@
     </row>
     <row r="20" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
         <v>20</v>
@@ -2299,7 +2323,7 @@
         <v>27</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="E20" t="s">
         <v>20</v>
@@ -2311,7 +2335,7 @@
         <v>20</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>21</v>
@@ -2335,7 +2359,7 @@
         <v>20</v>
       </c>
       <c r="P20" s="3">
-        <v>1152</v>
+        <v>2816</v>
       </c>
       <c r="Q20" t="s">
         <v>20</v>
@@ -2372,100 +2396,100 @@
       </c>
     </row>
     <row r="21" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="N21" s="2" t="s">
+      <c r="A21" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N21" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="O21" t="s">
-        <v>20</v>
-      </c>
-      <c r="P21" s="3">
-        <v>1024</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>20</v>
-      </c>
-      <c r="R21" t="s">
-        <v>20</v>
-      </c>
-      <c r="S21" t="s">
-        <v>20</v>
-      </c>
-      <c r="T21" t="s">
-        <v>20</v>
-      </c>
-      <c r="U21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="V21" t="s">
-        <v>20</v>
-      </c>
-      <c r="W21" t="s">
-        <v>20</v>
-      </c>
-      <c r="X21" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA21" s="2" t="s">
+      <c r="O21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="P21" s="8">
+        <v>2944</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>1</v>
+      </c>
+      <c r="R21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="S21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="T21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="U21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="V21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="X21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA21" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" t="s">
-        <v>20</v>
+        <v>71</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" t="s">
-        <v>20</v>
+        <v>27</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="E22" t="s">
         <v>20</v>
@@ -2501,7 +2525,7 @@
         <v>20</v>
       </c>
       <c r="P22" s="3">
-        <v>2560</v>
+        <v>3328</v>
       </c>
       <c r="Q22" t="s">
         <v>20</v>
@@ -2539,19 +2563,19 @@
     </row>
     <row r="23" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>63</v>
+        <v>29</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" t="s">
-        <v>20</v>
+        <v>30</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="3">
+        <v>64</v>
       </c>
       <c r="F23" t="s">
         <v>20</v>
@@ -2584,7 +2608,7 @@
         <v>20</v>
       </c>
       <c r="P23" s="3">
-        <v>2176</v>
+        <v>3072</v>
       </c>
       <c r="Q23" t="s">
         <v>20</v>
@@ -2622,19 +2646,19 @@
     </row>
     <row r="24" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B24" t="s">
-        <v>20</v>
+        <v>31</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" t="s">
-        <v>20</v>
+        <v>33</v>
+      </c>
+      <c r="D24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="3">
+        <v>512</v>
       </c>
       <c r="F24" t="s">
         <v>20</v>
@@ -2667,7 +2691,7 @@
         <v>20</v>
       </c>
       <c r="P24" s="3">
-        <v>768</v>
+        <v>128</v>
       </c>
       <c r="Q24" t="s">
         <v>20</v>
@@ -2705,19 +2729,19 @@
     </row>
     <row r="25" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B25" t="s">
         <v>20</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E25" t="s">
-        <v>20</v>
+        <v>33</v>
+      </c>
+      <c r="D25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="3">
+        <v>128</v>
       </c>
       <c r="F25" t="s">
         <v>20</v>
@@ -2726,7 +2750,7 @@
         <v>20</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>21</v>
@@ -2750,7 +2774,7 @@
         <v>20</v>
       </c>
       <c r="P25" s="3">
-        <v>2816</v>
+        <v>256</v>
       </c>
       <c r="Q25" t="s">
         <v>20</v>
@@ -2788,19 +2812,19 @@
     </row>
     <row r="26" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s">
         <v>20</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s">
         <v>20</v>
       </c>
-      <c r="E26" t="s">
-        <v>20</v>
+      <c r="E26" s="3">
+        <v>8</v>
       </c>
       <c r="F26" t="s">
         <v>20</v>
@@ -2833,7 +2857,7 @@
         <v>20</v>
       </c>
       <c r="P26" s="3">
-        <v>3200</v>
+        <v>1792</v>
       </c>
       <c r="Q26" t="s">
         <v>20</v>
@@ -2869,21 +2893,21 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" s="6" customFormat="1" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E27" t="s">
-        <v>20</v>
+        <v>33</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="3">
+        <v>8</v>
       </c>
       <c r="F27" t="s">
         <v>20</v>
@@ -2898,7 +2922,7 @@
         <v>21</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>21</v>
@@ -2916,10 +2940,10 @@
         <v>20</v>
       </c>
       <c r="P27" s="3">
-        <v>2944</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>1</v>
+        <v>1920</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>20</v>
       </c>
       <c r="R27" t="s">
         <v>20</v>
@@ -3037,16 +3061,16 @@
     </row>
     <row r="29" spans="1:27" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>72</v>
+        <v>41</v>
+      </c>
+      <c r="B29" t="s">
+        <v>20</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>72</v>
+        <v>42</v>
+      </c>
+      <c r="D29" t="s">
+        <v>20</v>
       </c>
       <c r="E29" t="s">
         <v>20</v>
@@ -3082,7 +3106,7 @@
         <v>20</v>
       </c>
       <c r="P29" s="3">
-        <v>3328</v>
+        <v>2304</v>
       </c>
       <c r="Q29" t="s">
         <v>20</v>
@@ -3119,6 +3143,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA29">
+    <sortCondition ref="C1:C29"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>